--- a/05_ML_Results/01_Metrics/ml_metrics.xlsx
+++ b/05_ML_Results/01_Metrics/ml_metrics.xlsx
@@ -408,13 +408,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0.948406025356519</v>
+        <v>0.6657376574969044</v>
       </c>
       <c r="C2">
-        <v>0.738090791347355</v>
+        <v>0.5086006521818925</v>
       </c>
       <c r="D2">
-        <v>0.9837147784012623</v>
+        <v>0.9921729105245939</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -422,13 +422,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>0.9658052961591225</v>
+        <v>0.9664517036388236</v>
       </c>
       <c r="C3">
-        <v>0.7053651970669519</v>
+        <v>0.7019863468172287</v>
       </c>
       <c r="D3">
-        <v>0.9961306170161106</v>
+        <v>0.9961703947207688</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -436,13 +436,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>0.9655043029441857</v>
+        <v>1.154047100093835</v>
       </c>
       <c r="C4">
-        <v>0.7479454626832113</v>
+        <v>0.8265269911060472</v>
       </c>
       <c r="D4">
-        <v>0.9972511374033768</v>
+        <v>0.9963031374851917</v>
       </c>
     </row>
   </sheetData>
